--- a/data/trans_orig/P1430-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1430-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cirrosis en 2012</t>
+          <t>Población con diagnóstico de cirrosis en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,97 +731,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,62 +1109,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6975</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6851</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680224</t>
+          <t>680631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>610255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1290491</t>
+          <t>1290367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>673756</t>
+          <t>674054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698567</t>
+          <t>699667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>708544</t>
+          <t>708549</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1377833</t>
+          <t>1377285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1388463</t>
+          <t>1388454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17629</t>
+          <t>17846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>25317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>596988</t>
+          <t>596771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609937</t>
+          <t>610335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>602176</t>
+          <t>602448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612140</t>
+          <t>612135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1204317</t>
+          <t>1203563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1220527</t>
+          <t>1220412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>21502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>414764</t>
+          <t>415053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428266</t>
+          <t>427331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>433835</t>
+          <t>434322</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445615</t>
+          <t>445686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>855706</t>
+          <t>855727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>870952</t>
+          <t>871877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>15169</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296851</t>
+          <t>296522</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307802</t>
+          <t>308713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>348746</t>
+          <t>348703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>648500</t>
+          <t>648613</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>661721</t>
+          <t>661729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247701</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>249851</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>377044</t>
+          <t>376704</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386851</t>
+          <t>386862</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>626905</t>
+          <t>626729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>636678</t>
+          <t>636726</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>37453</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33525</t>
+          <t>32609</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33743</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63517</t>
+          <t>63330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3388519</t>
+          <t>3389326</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3410975</t>
+          <t>3411220</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3521573</t>
+          <t>3522489</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3541246</t>
+          <t>3541217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6918360</t>
+          <t>6918547</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6948134</t>
+          <t>6948033</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cirrosis en 2016</t>
+          <t>Población con diagnóstico de cirrosis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3710,97 +3710,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5016</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5383</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6019</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4998</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390372</t>
+          <t>390739</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810220</t>
+          <t>809199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585244</t>
+          <t>586621</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>557200</t>
+          <t>557237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1146805</t>
+          <t>1146783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153161</t>
+          <t>1153160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655846</t>
+          <t>655433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667101</t>
+          <t>667067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>659479</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>661386</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1317132</t>
+          <t>1316695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328573</t>
+          <t>1328283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14569</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631479</t>
+          <t>632016</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644004</t>
+          <t>644010</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>642501</t>
+          <t>641709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1278680</t>
+          <t>1279590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1292009</t>
+          <t>1291263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>17950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>462117</t>
+          <t>461080</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474836</t>
+          <t>474772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>491017</t>
+          <t>491940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>958256</t>
+          <t>956817</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>971386</t>
+          <t>971488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>913</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>327057</t>
+          <t>326014</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>334330</t>
+          <t>333417</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>368736</t>
+          <t>369695</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>699972</t>
+          <t>700061</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>710036</t>
+          <t>710014</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251306</t>
+          <t>250573</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>386592</t>
+          <t>386364</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>398824</t>
+          <t>398814</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>641214</t>
+          <t>641932</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>654992</t>
+          <t>655193</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36530</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25979</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3357820</t>
+          <t>3358108</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3379354</t>
+          <t>3379345</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3519047</t>
+          <t>3520845</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3537273</t>
+          <t>3537277</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6885056</t>
+          <t>6885144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6912913</t>
+          <t>6911348</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1430-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1430-Edad-trans_orig.xlsx
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680631</t>
+          <t>680111</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1290367</t>
+          <t>1290561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>674054</t>
+          <t>673875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680906</t>
+          <t>680905</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>699667</t>
+          <t>699638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>708549</t>
+          <t>708580</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1377285</t>
+          <t>1377597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1388454</t>
+          <t>1388479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>11987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25317</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>596771</t>
+          <t>597702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>610335</t>
+          <t>609494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>602448</t>
+          <t>602277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612135</t>
+          <t>612126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1203563</t>
+          <t>1205961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1220412</t>
+          <t>1221373</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21502</t>
+          <t>21787</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>415053</t>
+          <t>415362</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427331</t>
+          <t>428277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>434322</t>
+          <t>435106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445686</t>
+          <t>445672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>855727</t>
+          <t>855442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871877</t>
+          <t>871900</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15169</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296522</t>
+          <t>296456</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>308713</t>
+          <t>308732</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>348703</t>
+          <t>348454</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>648613</t>
+          <t>649461</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>661729</t>
+          <t>661718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>376704</t>
+          <t>376030</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386862</t>
+          <t>386843</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>626729</t>
+          <t>625615</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>636726</t>
+          <t>636681</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32609</t>
+          <t>33293</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33844</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63330</t>
+          <t>63142</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3389326</t>
+          <t>3388523</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3411220</t>
+          <t>3411024</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3522489</t>
+          <t>3521805</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3541217</t>
+          <t>3540396</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6918547</t>
+          <t>6918735</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6948033</t>
+          <t>6947636</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390739</t>
+          <t>391217</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809199</t>
+          <t>810186</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>586621</t>
+          <t>586390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>557237</t>
+          <t>557904</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1146783</t>
+          <t>1146193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153160</t>
+          <t>1153162</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655433</t>
+          <t>654961</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667067</t>
+          <t>667090</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1316695</t>
+          <t>1316104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328283</t>
+          <t>1328508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,39 +4754,39 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2086</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7636</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7368</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>17296</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632016</t>
+          <t>632556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644010</t>
+          <t>644050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,42 +4867,42 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>646991</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>641441</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>649077</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>646991</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>641709</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>649077</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1279590</t>
+          <t>1277829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1291263</t>
+          <t>1291910</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>15151</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17950</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461080</t>
+          <t>462767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474772</t>
+          <t>475025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>491940</t>
+          <t>490963</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>956817</t>
+          <t>958506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>971488</t>
+          <t>971516</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12252</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>326014</t>
+          <t>326933</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333417</t>
+          <t>333411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>369695</t>
+          <t>369624</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>376785</t>
+          <t>376792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>700061</t>
+          <t>699840</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>710014</t>
+          <t>709996</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>15412</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250573</t>
+          <t>251087</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>386364</t>
+          <t>386854</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>398814</t>
+          <t>398826</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>641932</t>
+          <t>641755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>655193</t>
+          <t>654815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36242</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23697</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27544</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53748</t>
+          <t>55447</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3358108</t>
+          <t>3356976</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3379345</t>
+          <t>3378462</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3520845</t>
+          <t>3519774</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3537277</t>
+          <t>3537350</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6885144</t>
+          <t>6883445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6911348</t>
+          <t>6911277</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
